--- a/vch1101/files/kahoot/VCH1101_Kahoot_Unit3.xlsx
+++ b/vch1101/files/kahoot/VCH1101_Kahoot_Unit3.xlsx
@@ -712,12 +712,12 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
+          <t>，</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
           <t>、</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>，</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
+          <t>唔准帶，飲品入場。</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
           <t>唔准帶飲品入場。</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="inlineStr">
-        <is>
-          <t>唔准帶，飲品入場。</t>
         </is>
       </c>
       <c r="G10" s="25" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" s="1" t="n"/>
@@ -790,22 +790,22 @@
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
+          <t>丙</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>甲同行</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
           <t>甲</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>乙</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>丙</t>
-        </is>
-      </c>
-      <c r="F11" s="25" t="inlineStr">
-        <is>
-          <t>甲同行</t>
         </is>
       </c>
       <c r="G11" s="25" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" s="1" t="n"/>
@@ -829,17 +829,17 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
+          <t>同教練部開會</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>柯經理</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
           <t>6月10號下午兩點，</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>柯經理</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>同教練部開會</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
+          <t>刪走（客套口語）</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
           <t>必寫（工作事實）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>可選（補充說明）</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>刪走（客套口語）</t>
         </is>
       </c>
       <c r="F13" s="25" t="inlineStr"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -903,22 +903,22 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
+          <t>提出修繕保養需求</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>登記訂購詳情</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
           <t>辦理使用申請並記錄</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>記錄具體工作項目</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>提出修繕保養需求</t>
-        </is>
-      </c>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>登記訂購詳情</t>
         </is>
       </c>
       <c r="G14" s="25" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" s="1" t="n"/>
@@ -942,17 +942,17 @@
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
+          <t>寫金額</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>只寫「洗頭水等」「多樣」</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
           <t>分行逐項寫全名</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>只寫「洗頭水等」「多樣」</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="inlineStr">
-        <is>
-          <t>寫金額</t>
         </is>
       </c>
       <c r="F15" s="25" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -981,17 +981,17 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
+          <t>，</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
           <t>：</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>；</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>，</t>
         </is>
       </c>
       <c r="F16" s="25" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" s="1" t="n"/>
@@ -1020,17 +1020,17 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
+          <t>老細話明日，放假。</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>老細話明，日放假。</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
           <t>老細話：明日放假。</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>老細話明日，放假。</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>老細話明，日放假。</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -1059,22 +1059,22 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
+          <t>最後歸位，再用酒精噴器械，再抹淨。</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>抹淨器械，先用酒精噴，中途記得飲水。</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>用酒精噴器械，抹完就返屋企。</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
           <t>先用酒精噴器械，再抹淨，最後歸位。</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>最後歸位，再用酒精噴器械，再抹淨。</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>抹淨器械，先用酒精噴，中途記得飲水。</t>
-        </is>
-      </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>用酒精噴器械，抹完就返屋企。</t>
         </is>
       </c>
       <c r="G18" s="25" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
+          <t>阿Jay</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>主持咗</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
           <t>星期二上午，</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>阿Jay</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
-        <is>
-          <t>主持咗</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" s="1" t="n"/>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
+          <t>刪走（客套口語）</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
           <t>必寫（工作事實）</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>可選（補充說明）</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>刪走（客套口語）</t>
         </is>
       </c>
       <c r="F20" s="25" t="inlineStr"/>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -1172,22 +1172,22 @@
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
+          <t>提出修繕保養需求</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>記錄具體工作項目</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
           <t>登記訂購詳情</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>辦理使用申請並記錄</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>記錄具體工作項目</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>提出修繕保養需求</t>
         </is>
       </c>
       <c r="G21" s="25" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" s="1" t="n"/>
@@ -1216,17 +1216,17 @@
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
+          <t>5月1日</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>寫「一星期後」</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
           <t>4月21日</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>5月1日</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>寫「一星期後」</t>
         </is>
       </c>
       <c r="G22" s="25" t="n">
@@ -1250,22 +1250,22 @@
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
+          <t>，</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>；</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
           <t>：</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>，</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="F23" s="25" t="inlineStr">
         <is>
           <t>、</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="inlineStr">
-        <is>
-          <t>；</t>
         </is>
       </c>
       <c r="G23" s="25" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" s="1" t="n"/>
@@ -1289,22 +1289,22 @@
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
+          <t>剪髮唔收，錢係假㗎。</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>剪髮唔，收錢係假㗎。</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
           <t>剪髮唔收錢？係假㗎！</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
-        <is>
-          <t>剪髮唔收，錢係假㗎。</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="F24" s="25" t="inlineStr">
         <is>
           <t>剪髮唔收錢係，假㗎。</t>
-        </is>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>剪髮唔，收錢係假㗎。</t>
         </is>
       </c>
       <c r="G24" s="25" t="n">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" s="1" t="n"/>
@@ -1328,22 +1328,22 @@
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
+          <t>九點要領證，標籤要十二點前貼，展板就……你知啦。</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>佈展要早。標籤都要貼。展板擺好無？</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>佈展嗰日好忙，我哋九點到，領咗證，跟住擺展板，後來仲貼咗標籤，其實之前講過要早啲到。</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
           <t>佈展分三步：一、九點領工作證；二、十點前完成展板定位；三、十二點前貼好標籤。</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
-        <is>
-          <t>佈展嗰日好忙，我哋九點到，領咗證，跟住擺展板，後來仲貼咗標籤，其實之前講過要早啲到。</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
-        <is>
-          <t>九點要領證，標籤要十二點前貼，展板就……你知啦。</t>
-        </is>
-      </c>
-      <c r="F25" s="25" t="inlineStr">
-        <is>
-          <t>佈展要早。標籤都要貼。展板擺好無？</t>
         </is>
       </c>
       <c r="G25" s="25" t="n">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
+          <t>客人打嚟預約。</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
           <t>下午二點十分，</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>客人打嚟預約。</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr"/>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -1402,17 +1402,17 @@
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
+          <t>刪走（客套口語）</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>可選（補充說明）</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
           <t>必寫（工作事實）</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>可選（補充說明）</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>刪走（客套口語）</t>
         </is>
       </c>
       <c r="F27" s="25" t="inlineStr"/>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" s="1" t="n"/>
@@ -1437,22 +1437,22 @@
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
+          <t>登記訂購詳情</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>辦理使用申請並記錄</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>記錄具體工作項目</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
           <t>提出修繕保養需求</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>辦理使用申請並記錄</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>記錄具體工作項目</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>登記訂購詳情</t>
         </is>
       </c>
       <c r="G28" s="25" t="n">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
+          <t>寫採購部電話</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>唔使填</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
           <t>2667-8899</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>唔使填</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr">
         <is>
           <t>寫「見對白」</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="inlineStr">
-        <is>
-          <t>寫採購部電話</t>
         </is>
       </c>
       <c r="G29" s="25" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
